--- a/nail_artist_forms/020_nail_strips_inventory_order_form--nail_artist_forms.xlsx
+++ b/nail_artist_forms/020_nail_strips_inventory_order_form--nail_artist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Product Id</t>
+          <t>Product ID</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Form Id</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Form Id</t>
+          <t>Form ID 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,154 +934,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Form Id</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Form Id</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
